--- a/excel-files/QUEZON CITY/SAN JOSE ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/SAN JOSE ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6002301A-F7F3-43E8-B5AC-C612B920F5BB}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CBD336C-F0DE-41C2-9525-D4144E0245A2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5494,8 +5494,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5510,7 +5510,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13814,186 +13814,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61" name="Textbooks"/>
@@ -14011,8 +13831,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F43:F51 X112:X127 F63:F71 F73:F81 F53:F61 F33:F41 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F5:F12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R53:R54 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R55:R61 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G33:G41 M5:M12 Y5:Y12 G14:G21 G23:G31 G43:G51 G103:G110 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G5:G12" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14030,7 +13850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -22563,186 +22383,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65" name="Textbooks"/>
@@ -22760,8 +22400,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 Y21:Y29 G12:G19 M115:M122 S12:S19 M12:M19 M21:M29 G21:G29 Y12:Y19 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 G3:G10" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 F103:F113 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 X21:X29 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F3:F10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/QUEZON CITY/SAN JOSE ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/SAN JOSE ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CBD336C-F0DE-41C2-9525-D4144E0245A2}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12B5469A-18A2-FA41-A7D9-91DB58E44D9B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -320,7 +320,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1832,13 +1832,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1862,6 +1855,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2940,13 +2940,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2983,6 +2976,13 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3025,7 +3025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3042,7 +3042,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3098,7 +3098,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3471,17 +3471,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>300</v>
       </c>
       <c r="E5" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>9</v>
@@ -3619,7 +3619,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3639,12 +3639,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3720,19 +3720,25 @@
       <c r="C11" s="1">
         <v>194</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="1">
+        <v>240</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3754,12 +3760,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3781,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3825,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3869,7 +3875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.5">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3891,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3901,7 +3907,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3929,7 +3935,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3957,7 +3963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.5">
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3985,7 +3991,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -4013,7 +4019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4041,7 +4047,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4069,7 +4075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4097,29 +4103,27 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="1">
-        <v>276</v>
-      </c>
+      <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4129,19 +4133,25 @@
       <c r="C29" s="1">
         <v>276</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>300</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4151,7 +4161,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4161,19 +4171,25 @@
       <c r="C31" s="1">
         <v>208</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="D31" s="1">
+        <v>230</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4195,7 +4211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4217,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4239,7 +4255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4249,19 +4265,25 @@
       <c r="C35" s="1">
         <v>208</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="D35" s="1">
+        <v>230</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4271,19 +4293,25 @@
       <c r="C36" s="1">
         <v>208</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="D36" s="1">
+        <v>230</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4293,19 +4321,25 @@
       <c r="C37" s="1">
         <v>208</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="D37" s="1">
+        <v>230</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4315,19 +4349,25 @@
       <c r="C38" s="1">
         <v>208</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>230</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4349,7 +4389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4359,7 +4399,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4381,7 +4421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4403,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4425,7 +4465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4447,7 +4487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4469,7 +4509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4491,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4513,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4535,7 +4575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4557,7 +4597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4567,7 +4607,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4587,7 +4627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4607,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4627,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4647,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4667,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4687,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4707,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4727,7 +4767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4747,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4757,7 +4797,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4777,7 +4817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4797,7 +4837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4817,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4837,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4857,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4877,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4897,7 +4937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4917,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4937,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4947,7 +4987,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4967,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4987,7 +5027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -5007,7 +5047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -5027,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -5047,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -5067,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5087,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -5107,7 +5147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5127,7 +5167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5137,7 +5177,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5157,7 +5197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5177,7 +5217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5197,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5217,7 +5257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5237,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5257,7 +5297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5277,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5297,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5317,7 +5357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5327,7 +5367,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>25</v>
       </c>
@@ -5347,7 +5387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>25</v>
       </c>
@@ -5367,7 +5407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>25</v>
       </c>
@@ -5387,7 +5427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>25</v>
       </c>
@@ -5407,7 +5447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>25</v>
       </c>
@@ -5427,7 +5467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>25</v>
       </c>
@@ -5447,7 +5487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>25</v>
       </c>
@@ -5467,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>25</v>
       </c>
@@ -5497,7 +5537,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F91:F98 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5511,35 +5551,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
@@ -5573,7 +5613,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5656,7 +5696,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>62</v>
       </c>
@@ -5737,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5749,7 +5789,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="38.25">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5826,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5903,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5980,7 +6020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6057,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6134,7 +6174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6205,7 +6245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.5">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6276,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.5">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6347,7 +6387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6360,7 +6400,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="38.25">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6431,7 +6471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6502,7 +6542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6579,7 +6619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6656,7 +6696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6727,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6804,7 +6844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.5">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6881,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.5">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6952,7 +6992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6966,7 +7006,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="38.25">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7037,7 +7077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7108,7 +7148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7185,7 +7225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7262,7 +7302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7339,7 +7379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7416,7 +7456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7493,7 +7533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7570,7 +7610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7641,7 +7681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7655,7 +7695,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7732,7 +7772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7809,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.5">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7886,7 +7926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7963,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="38.25">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8040,7 +8080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8117,7 +8157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8194,7 +8234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8271,7 +8311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8354,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8368,7 +8408,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8445,7 +8485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8522,7 +8562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8599,7 +8639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8676,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8753,7 +8793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8824,7 +8864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8901,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8978,7 +9018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9055,7 +9095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -9069,7 +9109,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9140,7 +9180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9211,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9282,7 +9322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9353,7 +9393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="38.25">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9424,7 +9464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9495,7 +9535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.5">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9566,7 +9606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9637,7 +9677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9708,7 +9748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9722,7 +9762,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9791,7 +9831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9860,7 +9900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9929,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9998,7 +10038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -10067,7 +10107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10136,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10205,7 +10245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10274,7 +10314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10343,7 +10383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10357,7 +10397,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10426,7 +10466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10495,7 +10535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10564,7 +10604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10633,7 +10673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10702,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10771,7 +10811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10840,7 +10880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10909,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10978,7 +11018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10992,7 +11032,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -11061,7 +11101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11130,7 +11170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11199,7 +11239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11268,7 +11308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11337,7 +11377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11406,7 +11446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11475,7 +11515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11544,7 +11584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11613,7 +11653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11627,7 +11667,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11696,7 +11736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11765,7 +11805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11834,7 +11874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11903,7 +11943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11972,7 +12012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -12041,7 +12081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12110,7 +12150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -12179,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12248,7 +12288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12262,7 +12302,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>25</v>
       </c>
@@ -12331,7 +12371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>25</v>
       </c>
@@ -12400,7 +12440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>25</v>
       </c>
@@ -12469,7 +12509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>25</v>
       </c>
@@ -12538,7 +12578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>25</v>
       </c>
@@ -12607,7 +12647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>25</v>
       </c>
@@ -12676,7 +12716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -12745,7 +12785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>25</v>
       </c>
@@ -12814,7 +12854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12825,7 +12865,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12887,7 +12927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12949,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13011,7 +13051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13073,7 +13113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13135,7 +13175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13197,7 +13237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13259,7 +13299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13321,7 +13361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13383,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13445,7 +13485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13507,7 +13547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13569,7 +13609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13631,7 +13671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13693,7 +13733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13755,7 +13795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13851,34 +13891,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>34</v>
@@ -13913,7 +13953,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13996,7 +14036,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="35.25" customHeight="1">
+    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14073,7 +14113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14150,7 +14190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14227,7 +14267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14304,7 +14344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14381,7 +14421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14452,7 +14492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14523,7 +14563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14594,8 +14634,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" ht="15"/>
-    <row r="12" spans="1:27" ht="38.25">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14666,7 +14706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14737,7 +14777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14808,7 +14848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14879,7 +14919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14956,7 +14996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15033,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15110,7 +15150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15181,8 +15221,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="38.25">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15253,7 +15293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15324,7 +15364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15395,7 +15435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15466,7 +15506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15537,7 +15577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15614,7 +15654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15691,7 +15731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15768,7 +15808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15839,8 +15879,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15911,7 +15951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15982,7 +16022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16053,7 +16093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16124,7 +16164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16195,7 +16235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16266,7 +16306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16337,7 +16377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16408,7 +16448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16479,7 +16519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16556,7 +16596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16633,8 +16673,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16711,7 +16751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16782,7 +16822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16859,7 +16899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16930,7 +16970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -17001,7 +17041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17072,7 +17112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17143,7 +17183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17214,7 +17254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17285,7 +17325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17356,7 +17396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17427,8 +17467,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17511,7 +17551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17594,7 +17634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17677,7 +17717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17752,7 +17792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17829,7 +17869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17904,7 +17944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17979,7 +18019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -18054,7 +18094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18125,7 +18165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18200,7 +18240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -18279,8 +18319,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18349,7 +18389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18418,7 +18458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18487,7 +18527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18556,7 +18596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18625,7 +18665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18694,7 +18734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18763,7 +18803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18832,7 +18872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18901,7 +18941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18970,7 +19010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -19039,8 +19079,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -19109,7 +19149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19178,7 +19218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19247,7 +19287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -19316,7 +19356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19385,7 +19425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19454,7 +19494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19523,7 +19563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19592,7 +19632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19661,7 +19701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19730,7 +19770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19799,8 +19839,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19869,7 +19909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19938,7 +19978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -20007,7 +20047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -20076,7 +20116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -20145,7 +20185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20214,7 +20254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -20283,7 +20323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20352,7 +20392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20421,7 +20461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20490,7 +20530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20559,8 +20599,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20629,7 +20669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20698,7 +20738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20767,7 +20807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20836,7 +20876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20905,7 +20945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20974,7 +21014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -21043,7 +21083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -21112,7 +21152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -21181,7 +21221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -21250,7 +21290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21319,8 +21359,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>25</v>
       </c>
@@ -21389,7 +21429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>25</v>
       </c>
@@ -21458,7 +21498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>25</v>
       </c>
@@ -21527,7 +21567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>25</v>
       </c>
@@ -21596,7 +21636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>25</v>
       </c>
@@ -21665,7 +21705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>25</v>
       </c>
@@ -21734,7 +21774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>25</v>
       </c>
@@ -21803,7 +21843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>25</v>
       </c>
@@ -21872,8 +21912,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21903,7 +21943,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21933,7 +21973,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21963,7 +22003,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21993,7 +22033,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -22023,7 +22063,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -22053,7 +22093,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -22083,7 +22123,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -22113,7 +22153,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -22143,7 +22183,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -22173,7 +22213,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -22203,7 +22243,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -22233,7 +22273,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -22263,7 +22303,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -22293,7 +22333,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -22323,7 +22363,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -22353,7 +22393,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
